--- a/scripts_classification/07-analysis_results/all-results.xlsx
+++ b/scripts_classification/07-analysis_results/all-results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yoom618/Library/Mobile Documents/com~apple~CloudDocs/00-Paper/06-TSC/논문 작성/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51398E1-DB80-EE4E-81E1-DE8C78A15BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303F0E13-40C1-C942-B96B-5DEA2A44F1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26880" windowHeight="18880" xr2:uid="{7126E587-7C11-DA4B-85ED-BD322243169B}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26880" windowHeight="16860" xr2:uid="{7126E587-7C11-DA4B-85ED-BD322243169B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -922,7 +922,7 @@
         <v>78.536585365853668</v>
       </c>
       <c r="V5">
-        <v>80</v>
+        <v>80.487804878048806</v>
       </c>
     </row>
     <row r="6" spans="1:22">
